--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104658_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104658_W23.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7863</v>
+        <v>5.6808</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8494</v>
+        <v>5.0769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9369</v>
+        <v>0.6039</v>
       </c>
       <c r="G2" t="n">
-        <v>1.836</v>
+        <v>1.8468</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4832</v>
+        <v>3.4865</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.6472</v>
+        <v>-1.6397</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5884</v>
+        <v>3.5616</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7058</v>
+        <v>3.6887</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1174</v>
+        <v>-0.127</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7524</v>
+        <v>-1.7148</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5299</v>
+        <v>-1.5127</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4966</v>
+        <v>0.3787</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.378</v>
+        <v>-0.1189</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8746</v>
+        <v>0.4977</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0424</v>
+        <v>3.4069</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6513</v>
+        <v>3.096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3912</v>
+        <v>0.3109</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0883</v>
+        <v>2.0815</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0002</v>
+        <v>1.9827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0881</v>
+        <v>0.0988</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0989</v>
+        <v>4.0598</v>
       </c>
       <c r="K3" t="n">
-        <v>3.875</v>
+        <v>3.8363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0106</v>
+        <v>-1.9783</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2756</v>
+        <v>0.641</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9115</v>
+        <v>0.4036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3641</v>
+        <v>0.2374</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2581</v>
+        <v>1.5034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5373</v>
+        <v>0.7652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7208</v>
+        <v>0.7382</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1935</v>
+        <v>0.198</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5556</v>
+        <v>-0.5544</v>
       </c>
       <c r="I4" t="n">
-        <v>0.749</v>
+        <v>0.7524</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1634</v>
+        <v>1.1556</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9699</v>
+        <v>-0.9576</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5232</v>
+        <v>-0.2881</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1028</v>
+        <v>0.1024</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0102</v>
+        <v>1.2958</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9737</v>
+        <v>2.8704</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9634</v>
+        <v>-1.5746</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4877</v>
+        <v>2.4705</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6016</v>
+        <v>-0.6112</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0893</v>
+        <v>3.0817</v>
       </c>
       <c r="J5" t="n">
-        <v>4.552</v>
+        <v>4.504</v>
       </c>
       <c r="K5" t="n">
-        <v>0.266</v>
+        <v>0.2371</v>
       </c>
       <c r="L5" t="n">
-        <v>4.286</v>
+        <v>4.2669</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0643</v>
+        <v>-2.0335</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.587</v>
+        <v>-0.2916</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6049</v>
+        <v>-0.6532</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0178</v>
+        <v>0.3616</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6932</v>
       </c>
       <c r="E6" t="n">
-        <v>0.881</v>
+        <v>0.8719</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.314</v>
+        <v>-0.1788</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.152</v>
+        <v>-0.1503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0852</v>
+        <v>0.0834</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2372</v>
+        <v>-0.2337</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1603</v>
+        <v>-0.1664</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2129</v>
+        <v>-0.0882</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1615</v>
+        <v>-0.037</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GANAL</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8994</v>
+        <v>0.0095</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9104</v>
+        <v>-0.8142</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0109</v>
+        <v>0.8236</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0023</v>
+        <v>-0.9776</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7645</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2159</v>
+        <v>-0.2131</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7864</v>
+        <v>0.8704</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7864</v>
+        <v>0.7444</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1259</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2159</v>
+        <v>-1.848</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.5089</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2159</v>
+        <v>-0.3391</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6472</v>
+        <v>-0.3787</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6472</v>
+        <v>-0.5464</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1677</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.966</v>
+        <v>-1.3379</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7504</v>
+        <v>-0.7966</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7844</v>
+        <v>-0.5413</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9842</v>
+        <v>3.3392</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7736</v>
+        <v>0.7416</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2106</v>
+        <v>2.5976</v>
       </c>
       <c r="J8" t="n">
-        <v>0.896</v>
+        <v>4.2817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7548</v>
+        <v>1.2885</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1411</v>
+        <v>2.9932</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8801</v>
+        <v>-0.9425</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5284</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3517</v>
+        <v>-0.3956</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-6.8289</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>2.7316</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3428</v>
+        <v>-0.1928</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5122</v>
+        <v>-0.7438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1693</v>
+        <v>0.551</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>A. GANAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.509</v>
+        <v>-1.3739</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0241</v>
+        <v>-1.3871</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.485</v>
+        <v>0.0132</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4457</v>
+        <v>-1.0041</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6754</v>
+        <v>-0.7896</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7703</v>
+        <v>-0.2144</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6944</v>
+        <v>-0.7896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>-0.7896</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7513</v>
+        <v>-0.2144</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6927</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0586</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4243</v>
+        <v>0.1765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3297</v>
+        <v>0.1765</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1018</v>
+        <v>-1.4092</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3163</v>
+        <v>-1.0279</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7855</v>
+        <v>-0.3813</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3576</v>
+        <v>-1.4439</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7534</v>
+        <v>-0.6722</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6042</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3368</v>
+        <v>-0.6979</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3223</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0145</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9792</v>
+        <v>-0.746</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5689</v>
+        <v>-0.6895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4104</v>
+        <v>-0.0565</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.083</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.805</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9908</v>
+        <v>-0.3311</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3549</v>
+        <v>-0.33</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3641</v>
+        <v>-0.0011</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8924</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5669</v>
+        <v>-2.4144</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1038</v>
+        <v>-0.0506</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4631</v>
+        <v>-2.3638</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.627</v>
+        <v>-1.6176</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2308</v>
+        <v>0.2353</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8578</v>
+        <v>-1.8529</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2823</v>
+        <v>-0.3012</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0665</v>
+        <v>1.0547</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3488</v>
+        <v>-1.3559</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3447</v>
+        <v>-1.3164</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1155</v>
+        <v>0.0163</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1785</v>
+        <v>0.2505</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.294</v>
+        <v>-0.2342</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4749</v>
+        <v>-4.6783</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2485</v>
+        <v>-5.1578</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7736</v>
+        <v>0.4795</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7449</v>
+        <v>-2.7459</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7186</v>
+        <v>-1.7148</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0263</v>
+        <v>-1.031</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5991</v>
+        <v>-2.6187</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4342</v>
+        <v>-1.4414</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1458</v>
+        <v>-0.1271</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0847</v>
+        <v>-0.1114</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3811</v>
+        <v>-0.2627</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4657</v>
+        <v>0.1513</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2272</v>
+        <v>-5.7627</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6443</v>
+        <v>-3.1983</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5828</v>
+        <v>-2.5645</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5002</v>
+        <v>-4.5037</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0692</v>
+        <v>-2.068</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.431</v>
+        <v>-2.4357</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.745</v>
+        <v>-1.7672</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1398</v>
+        <v>-1.1484</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6052</v>
+        <v>-0.6188</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7552</v>
+        <v>-2.7365</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0465</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.081200000000001</v>
+        <v>-4.3868</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1050999999999971</v>
+        <v>0.2479000000000009</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.975999999999999</v>
+        <v>-4.635</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.4932</v>
+        <v>-2.5071</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6275999999999997</v>
+        <v>-0.6452000000000007</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.865699999999999</v>
+        <v>-1.8617</v>
       </c>
       <c r="J14" t="n">
-        <v>12.368</v>
+        <v>12.0921</v>
       </c>
       <c r="K14" t="n">
-        <v>6.784599999999999</v>
+        <v>6.6149</v>
       </c>
       <c r="L14" t="n">
-        <v>5.583299999999999</v>
+        <v>5.477000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.8612</v>
+        <v>-14.5991</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.4118</v>
+        <v>-7.2602</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.449200000000001</v>
+        <v>-7.338900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7389</v>
+        <v>-1.0455</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.2663</v>
+        <v>-2.5589</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5269</v>
+        <v>1.5136</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.1171</v>
+        <v>-3.1106</v>
       </c>
       <c r="W14" t="n">
-        <v>4.4031</v>
+        <v>4.3729</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.520199999999999</v>
+        <v>-7.4833</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5577</v>
+        <v>6.0127</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4845</v>
+        <v>6.1072</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.0945</v>
       </c>
       <c r="G15" t="n">
-        <v>3.987</v>
+        <v>3.9612</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7778</v>
+        <v>0.7729</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2091</v>
+        <v>3.1883</v>
       </c>
       <c r="J15" t="n">
-        <v>6.7039</v>
+        <v>6.6393</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8662</v>
+        <v>1.8369</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8376</v>
+        <v>4.8025</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7169</v>
+        <v>-2.6781</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0884</v>
+        <v>-1.064</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6392</v>
+        <v>-0.1487</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0948</v>
+        <v>-0.386</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5444</v>
+        <v>0.2374</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W15" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1962</v>
+        <v>5.0203</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6721</v>
+        <v>3.3202</v>
       </c>
       <c r="F16" t="n">
-        <v>1.524</v>
+        <v>1.7001</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8675</v>
+        <v>2.8693</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4258</v>
+        <v>0.4169</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4417</v>
+        <v>2.4524</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8945</v>
+        <v>3.8551</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3569</v>
+        <v>1.323</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5375</v>
+        <v>2.5321</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0269</v>
+        <v>-0.9858</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9311</v>
+        <v>-0.9061</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7906</v>
+        <v>0.0419</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4608</v>
+        <v>-0.7531</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6702</v>
+        <v>0.795</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.822</v>
+        <v>2.6938</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8595</v>
+        <v>0.6565</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9625</v>
+        <v>2.0373</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3867</v>
+        <v>2.4463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1601</v>
+        <v>0.4934</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2266</v>
+        <v>1.953</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8202</v>
+        <v>1.6255</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>0.9156</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4335</v>
+        <v>0.8208</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4735</v>
+        <v>-0.2166</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04</v>
+        <v>1.0374</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2765</v>
+        <v>-0.663</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1735</v>
+        <v>-0.969</v>
       </c>
       <c r="U17" t="n">
-        <v>1.103</v>
+        <v>0.306</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5743</v>
+        <v>1.633</v>
       </c>
       <c r="E18" t="n">
-        <v>0.326</v>
+        <v>0.0223</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2483</v>
+        <v>1.6107</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4329</v>
+        <v>0.3946</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4818</v>
+        <v>0.1635</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9512</v>
+        <v>0.2311</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6477</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7202</v>
+        <v>0.6238</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9275</v>
+        <v>0.1862</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7852</v>
+        <v>-0.4154</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2384</v>
+        <v>-0.4603</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0237</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.766</v>
+        <v>1.0791</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3217</v>
+        <v>0.3505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4443</v>
+        <v>0.7286</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0558</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1355</v>
+        <v>-0.0649</v>
       </c>
       <c r="F19" t="n">
-        <v>0.127</v>
+        <v>0.1207</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9243</v>
+        <v>0.0035</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2526</v>
+        <v>-0.0144</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6717</v>
+        <v>0.018</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3654</v>
+        <v>0.0745</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3463</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.599</v>
+        <v>-0.0144</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4621</v>
+        <v>0.0523</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2299</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2323</v>
+        <v>0.1917</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0111</v>
+        <v>-0.2877</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0645</v>
+        <v>-0.4938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0534</v>
+        <v>0.206</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0159</v>
+        <v>-0.2446</v>
       </c>
       <c r="I20" t="n">
-        <v>0.016</v>
+        <v>-0.6703</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0746</v>
+        <v>-0.3704</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.3447</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0745</v>
+        <v>-0.5444</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0159</v>
+        <v>-0.5893</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0586</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0112</v>
+        <v>0.1718</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1391</v>
+        <v>-0.1233</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1279</v>
+        <v>0.2951</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3125</v>
+        <v>-0.4177</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6707</v>
+        <v>-1.938</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3583</v>
+        <v>1.5203</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5964</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3012</v>
+        <v>0.3056</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5525</v>
+        <v>-0.5742</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0438</v>
+        <v>-0.0109</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3254</v>
+        <v>0.2162</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0575</v>
+        <v>-0.1769</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2679</v>
+        <v>0.3931</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0502</v>
+        <v>-0.7952</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7751</v>
+        <v>-1.3219</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8253</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4751</v>
+        <v>-1.435</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5439</v>
+        <v>0.0056</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0688</v>
+        <v>-1.4406</v>
       </c>
       <c r="J22" t="n">
-        <v>3.598</v>
+        <v>-1.5076</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4114</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1866</v>
+        <v>-1.542</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1229</v>
+        <v>0.0725</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8675</v>
+        <v>-0.0289</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2554</v>
+        <v>0.1014</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1364</v>
+        <v>0.1846</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2389</v>
+        <v>0.1857</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3753</v>
+        <v>-0.0011</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3422</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4498</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4409</v>
+        <v>-1.0595</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5522</v>
+        <v>1.7479</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1113</v>
+        <v>-2.8074</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4339</v>
+        <v>1.4918</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0028</v>
+        <v>2.5473</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4368</v>
+        <v>-1.0556</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5008</v>
+        <v>3.5818</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>3.3957</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5354</v>
+        <v>0.1862</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0669</v>
+        <v>-2.0901</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0318</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4606</v>
+        <v>0.1057</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0514</v>
+        <v>-0.2374</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4092</v>
+        <v>0.343</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-3.3399</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2938</v>
+        <v>-2.1284</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4551</v>
+        <v>-0.6883</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8387</v>
+        <v>-1.4401</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.8469</v>
+        <v>-1.8437</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2075</v>
+        <v>-0.3825</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6395</v>
+        <v>-1.4612</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7059</v>
+        <v>1.2376</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3241</v>
+        <v>0.7239</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6181</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.141</v>
+        <v>-3.0813</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8834</v>
+        <v>-1.1064</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2576</v>
+        <v>-1.9749</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3036</v>
+        <v>0.7153</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5606</v>
+        <v>0.3505</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7429</v>
+        <v>0.3648</v>
       </c>
       <c r="V24" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0285</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9519</v>
+        <v>-4.0639</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2632</v>
+        <v>-2.7123</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6887</v>
+        <v>-1.3515</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.8545</v>
+        <v>-3.881</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3912</v>
+        <v>-2.2222</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4634</v>
+        <v>-1.6588</v>
       </c>
       <c r="J25" t="n">
-        <v>1.247</v>
+        <v>-0.7724</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7272999999999999</v>
+        <v>-1.3594</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.587</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.1016</v>
+        <v>-3.1086</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1185</v>
+        <v>-0.8628</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.9831</v>
+        <v>-2.2458</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0974</v>
+        <v>1.5667</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2419</v>
+        <v>0.3851</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1446</v>
+        <v>1.1817</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5463</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5463</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.081299999999997</v>
+        <v>6.6632</v>
       </c>
       <c r="E26" t="n">
-        <v>4.975999999999997</v>
+        <v>4.634899999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1052</v>
+        <v>2.028300000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>2.4933</v>
+        <v>2.507</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6274000000000002</v>
+        <v>0.6452000000000004</v>
       </c>
       <c r="I26" t="n">
-        <v>1.865600000000001</v>
+        <v>1.8619</v>
       </c>
       <c r="J26" t="n">
-        <v>14.8613</v>
+        <v>14.5992</v>
       </c>
       <c r="K26" t="n">
-        <v>7.411899999999999</v>
+        <v>7.260400000000002</v>
       </c>
       <c r="L26" t="n">
-        <v>7.4491</v>
+        <v>7.339</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.368</v>
+        <v>-12.0923</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.784599999999999</v>
+        <v>-6.6151</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.5835</v>
+        <v>-5.477</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6101</v>
+        <v>13.658</v>
       </c>
       <c r="S26" t="n">
-        <v>1.739</v>
+        <v>3.3219</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.527100000000001</v>
+        <v>-1.5133</v>
       </c>
       <c r="U26" t="n">
-        <v>3.2662</v>
+        <v>4.8353</v>
       </c>
       <c r="V26" t="n">
-        <v>3.1174</v>
+        <v>3.110700000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.5204</v>
+        <v>7.4835</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.403</v>
+        <v>-4.3727</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104658_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104658_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.4833</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104658_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.3727</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
